--- a/Catch and index models/Sintese_3_modelos/tabela_status_modelo_familia.xlsx
+++ b/Catch and index models/Sintese_3_modelos/tabela_status_modelo_familia.xlsx
@@ -55,7 +55,7 @@
     <t>NN-CMSY++</t>
   </si>
   <si>
-    <t>0,70 – 0,77</t>
+    <t>0,69 – 0,75</t>
   </si>
   <si>
     <t>0,20</t>
@@ -73,7 +73,7 @@
     <t>zBRT</t>
   </si>
   <si>
-    <t>1,30 – 1,43</t>
+    <t>1,31 – 1,43</t>
   </si>
   <si>
     <t>0,10 – 0,11</t>
@@ -85,7 +85,7 @@
     <t>Mudança de alvo</t>
   </si>
   <si>
-    <t>1,41 – 1,57</t>
+    <t>1,42 – 1,56</t>
   </si>
   <si>
     <t>0,09 – 0,10</t>
